--- a/framework/data/excel/search_hybrid.xlsx
+++ b/framework/data/excel/search_hybrid.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\_DA\DA4\framework\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\_DA\DA4\framework\data\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B62697A9-0AAE-4C59-A407-6726465B9CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E8ABF0F-BAC6-4E6D-9672-7B533453883E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="18240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2070" yWindow="3795" windowWidth="12450" windowHeight="13185" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="search_hybrid" sheetId="1" r:id="rId1"/>
-    <sheet name="search_data" sheetId="2" r:id="rId2"/>
+    <sheet name="test_cases" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>

--- a/framework/data/excel/search_hybrid.xlsx
+++ b/framework/data/excel/search_hybrid.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\_DA\DA4\framework\data\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E8ABF0F-BAC6-4E6D-9672-7B533453883E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5369FD6F-8A59-487A-9AF2-8D8157E1913F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2070" yWindow="3795" windowWidth="12450" windowHeight="13185" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="search_hybrid" sheetId="1" r:id="rId1"/>
+    <sheet name="test_steps" sheetId="1" r:id="rId1"/>
     <sheet name="test_cases" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
